--- a/Excel/SkillRuneConfig.xlsx
+++ b/Excel/SkillRuneConfig.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WrittenLegend\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowHeight="17680" activeTab="5"/>
   </bookViews>
@@ -2058,12 +2063,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/Excel/SkillRuneConfig.xlsx
+++ b/Excel/SkillRuneConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="5"/>
+    <workbookView windowHeight="17680" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="批量配置" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="暗金" sheetId="4" r:id="rId4"/>
     <sheet name="混沌" sheetId="5" r:id="rId5"/>
     <sheet name="虚无" sheetId="6" r:id="rId6"/>
+    <sheet name="寂灭" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -558,8 +559,86 @@
 </comments>
 </file>
 
+<file path=xl/comments7.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>admin</author>
+  </authors>
+  <commentList>
+    <comment ref="C3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+ID* 10 + level
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+攻击力系数（百分比），额外附加固定伤害值</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="T3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+0 以自己为圆心
+1 距离1格</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2231" uniqueCount="440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2378" uniqueCount="492">
   <si>
     <t>_ID</t>
   </si>
@@ -1830,6 +1909,12 @@
     <t>落雷术·天目Ⅱ</t>
   </si>
   <si>
+    <t>冰爆术·天目Ⅱ</t>
+  </si>
+  <si>
+    <t>此技能额外增加50%命中</t>
+  </si>
+  <si>
     <t>魔尊附体·破限Ⅱ</t>
   </si>
   <si>
@@ -1879,6 +1964,156 @@
   </si>
   <si>
     <t>白虎额外增加25%命中</t>
+  </si>
+  <si>
+    <t>基础剑术·导师</t>
+  </si>
+  <si>
+    <t>提高此技能系数40%系数增幅</t>
+  </si>
+  <si>
+    <t>流光剑法·导师</t>
+  </si>
+  <si>
+    <t>旋风斩·导师</t>
+  </si>
+  <si>
+    <t>腾空斩·导师</t>
+  </si>
+  <si>
+    <t>武神盾·导师</t>
+  </si>
+  <si>
+    <t>武力精通·导师</t>
+  </si>
+  <si>
+    <t>烈焰斩·导师</t>
+  </si>
+  <si>
+    <t>战吼·导师</t>
+  </si>
+  <si>
+    <t>裂天斩·导师</t>
+  </si>
+  <si>
+    <t>裂地斩·导师</t>
+  </si>
+  <si>
+    <t>战士之魂·导师</t>
+  </si>
+  <si>
+    <t>剑二十三·导师</t>
+  </si>
+  <si>
+    <t>提高此技能系数30%系数增幅</t>
+  </si>
+  <si>
+    <t>流光剑法·天目Ⅲ</t>
+  </si>
+  <si>
+    <t>此技能额外增加40%命中</t>
+  </si>
+  <si>
+    <t>裂地斩·天目Ⅲ</t>
+  </si>
+  <si>
+    <t>剑二十三·天目Ⅲ</t>
+  </si>
+  <si>
+    <t>火球术·导师</t>
+  </si>
+  <si>
+    <t>落雷术·导师</t>
+  </si>
+  <si>
+    <t>火焰墙·导师</t>
+  </si>
+  <si>
+    <t>烈焰环·导师</t>
+  </si>
+  <si>
+    <t>法力盾·导师</t>
+  </si>
+  <si>
+    <t>法术精通·导师</t>
+  </si>
+  <si>
+    <t>冰爆术·导师</t>
+  </si>
+  <si>
+    <t>心灵传送·导师</t>
+  </si>
+  <si>
+    <t>毁灭流星·导师</t>
+  </si>
+  <si>
+    <t>分身术·导师</t>
+  </si>
+  <si>
+    <t>法师之魂·导师</t>
+  </si>
+  <si>
+    <t>魔尊附体·导师</t>
+  </si>
+  <si>
+    <t>落雷术·天目Ⅲ</t>
+  </si>
+  <si>
+    <t>冰爆术·天目Ⅲ</t>
+  </si>
+  <si>
+    <t>此技能额外增加100%命中</t>
+  </si>
+  <si>
+    <t>魔尊附体·破限Ⅲ</t>
+  </si>
+  <si>
+    <t>增加50层叠加上限</t>
+  </si>
+  <si>
+    <t>疗伤术·导师</t>
+  </si>
+  <si>
+    <t>驱魔符·导师</t>
+  </si>
+  <si>
+    <t>毒咒术·导师</t>
+  </si>
+  <si>
+    <t>召唤小兵·导师</t>
+  </si>
+  <si>
+    <t>道力盾·导师</t>
+  </si>
+  <si>
+    <t>道力精通·导师</t>
+  </si>
+  <si>
+    <t>召唤魔兽·导师</t>
+  </si>
+  <si>
+    <t>隐身道法·导师</t>
+  </si>
+  <si>
+    <t>召唤月神·导师</t>
+  </si>
+  <si>
+    <t>无极道体·导师</t>
+  </si>
+  <si>
+    <t>道士之魂·导师</t>
+  </si>
+  <si>
+    <t>召唤白虎·导师</t>
+  </si>
+  <si>
+    <t>驱魔符·天目Ⅲ</t>
+  </si>
+  <si>
+    <t>召唤白虎·天目Ⅲ</t>
+  </si>
+  <si>
+    <t>白虎额外增加30%命中</t>
   </si>
 </sst>
 </file>
@@ -16515,7 +16750,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:U58"/>
+  <dimension ref="C3:U59"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -17928,13 +18163,13 @@
     </row>
     <row r="40" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C40" s="1">
-        <v>42112</v>
+        <v>42107</v>
       </c>
       <c r="D40" s="1">
         <v>6</v>
       </c>
       <c r="E40" s="1">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="F40" s="1">
         <v>5</v>
@@ -17943,7 +18178,7 @@
         <v>2</v>
       </c>
       <c r="H40" s="3">
-        <v>2012</v>
+        <v>2007</v>
       </c>
       <c r="I40" s="1">
         <v>0</v>
@@ -17966,83 +18201,86 @@
       <c r="O40" s="1">
         <v>10</v>
       </c>
-      <c r="R40" s="1">
+      <c r="P40" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="41" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="C41" s="1">
+        <v>42112</v>
+      </c>
+      <c r="D41" s="1">
+        <v>6</v>
+      </c>
+      <c r="E41" s="1">
+        <v>10</v>
+      </c>
+      <c r="F41" s="1">
+        <v>5</v>
+      </c>
+      <c r="G41" s="1">
+        <v>2</v>
+      </c>
+      <c r="H41" s="3">
+        <v>2012</v>
+      </c>
+      <c r="I41" s="1">
+        <v>0</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="K41" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="L41" s="1">
+        <v>4</v>
+      </c>
+      <c r="M41" s="1">
+        <v>0</v>
+      </c>
+      <c r="N41" s="1">
+        <v>10</v>
+      </c>
+      <c r="O41" s="1">
+        <v>10</v>
+      </c>
+      <c r="R41" s="1">
         <v>40</v>
       </c>
-    </row>
-    <row r="41" s="1" customFormat="1" customHeight="1" spans="3:18">
-      <c r="H41" s="3"/>
-      <c r="J41" s="3"/>
     </row>
     <row r="42" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="H42" s="3"/>
       <c r="J42" s="3"/>
     </row>
     <row r="43" s="1" customFormat="1" customHeight="1" spans="3:18">
-      <c r="C43" s="1">
-        <v>43001</v>
-      </c>
-      <c r="D43" s="1">
-        <v>6</v>
-      </c>
-      <c r="E43" s="1">
-        <v>300</v>
-      </c>
-      <c r="F43" s="1">
-        <v>500</v>
-      </c>
-      <c r="G43" s="1">
-        <v>3</v>
-      </c>
-      <c r="H43" s="3">
-        <v>3001</v>
-      </c>
-      <c r="I43" s="1">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>425</v>
-      </c>
-      <c r="K43" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="L43" s="1">
-        <v>6</v>
-      </c>
-      <c r="M43" s="1">
-        <v>25</v>
-      </c>
-      <c r="N43" s="1">
-        <v>10</v>
-      </c>
-      <c r="O43" s="1">
-        <v>10</v>
-      </c>
+      <c r="H43" s="3"/>
+      <c r="J43" s="3"/>
     </row>
     <row r="44" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C44" s="1">
-        <v>43002</v>
+        <v>43001</v>
       </c>
       <c r="D44" s="1">
         <v>6</v>
       </c>
       <c r="E44" s="1">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="F44" s="1">
-        <v>25</v>
+        <v>500</v>
       </c>
       <c r="G44" s="1">
         <v>3</v>
       </c>
       <c r="H44" s="3">
-        <v>3002</v>
+        <v>3001</v>
       </c>
       <c r="I44" s="1">
         <v>0</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="K44" s="1" t="s">
         <v>394</v>
@@ -18062,28 +18300,28 @@
     </row>
     <row r="45" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C45" s="1">
-        <v>43003</v>
+        <v>43002</v>
       </c>
       <c r="D45" s="1">
         <v>6</v>
       </c>
       <c r="E45" s="1">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="F45" s="1">
-        <v>500</v>
+        <v>25</v>
       </c>
       <c r="G45" s="1">
         <v>3</v>
       </c>
       <c r="H45" s="3">
-        <v>3003</v>
+        <v>3002</v>
       </c>
       <c r="I45" s="1">
         <v>0</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="K45" s="1" t="s">
         <v>394</v>
@@ -18103,7 +18341,7 @@
     </row>
     <row r="46" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C46" s="1">
-        <v>43004</v>
+        <v>43003</v>
       </c>
       <c r="D46" s="1">
         <v>6</v>
@@ -18118,13 +18356,13 @@
         <v>3</v>
       </c>
       <c r="H46" s="3">
-        <v>3004</v>
+        <v>3003</v>
       </c>
       <c r="I46" s="1">
         <v>0</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="K46" s="1" t="s">
         <v>394</v>
@@ -18144,28 +18382,28 @@
     </row>
     <row r="47" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C47" s="1">
-        <v>43005</v>
+        <v>43004</v>
       </c>
       <c r="D47" s="1">
         <v>6</v>
       </c>
       <c r="E47" s="1">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="F47" s="1">
-        <v>25</v>
+        <v>500</v>
       </c>
       <c r="G47" s="1">
         <v>3</v>
       </c>
       <c r="H47" s="3">
-        <v>3005</v>
+        <v>3004</v>
       </c>
       <c r="I47" s="1">
         <v>0</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="K47" s="1" t="s">
         <v>394</v>
@@ -18185,13 +18423,13 @@
     </row>
     <row r="48" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C48" s="1">
-        <v>43006</v>
+        <v>43005</v>
       </c>
       <c r="D48" s="1">
         <v>6</v>
       </c>
       <c r="E48" s="1">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="F48" s="1">
         <v>25</v>
@@ -18200,13 +18438,13 @@
         <v>3</v>
       </c>
       <c r="H48" s="3">
-        <v>3006</v>
+        <v>3005</v>
       </c>
       <c r="I48" s="1">
         <v>0</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="K48" s="1" t="s">
         <v>394</v>
@@ -18226,28 +18464,28 @@
     </row>
     <row r="49" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C49" s="1">
-        <v>43007</v>
+        <v>43006</v>
       </c>
       <c r="D49" s="1">
         <v>6</v>
       </c>
       <c r="E49" s="1">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="F49" s="1">
-        <v>500</v>
+        <v>25</v>
       </c>
       <c r="G49" s="1">
         <v>3</v>
       </c>
       <c r="H49" s="3">
-        <v>3007</v>
+        <v>3006</v>
       </c>
       <c r="I49" s="1">
         <v>0</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="K49" s="1" t="s">
         <v>394</v>
@@ -18267,28 +18505,28 @@
     </row>
     <row r="50" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C50" s="1">
-        <v>43008</v>
+        <v>43007</v>
       </c>
       <c r="D50" s="1">
         <v>6</v>
       </c>
       <c r="E50" s="1">
-        <v>50</v>
+        <v>300</v>
       </c>
       <c r="F50" s="1">
-        <v>10</v>
+        <v>500</v>
       </c>
       <c r="G50" s="1">
         <v>3</v>
       </c>
       <c r="H50" s="3">
-        <v>3008</v>
+        <v>3007</v>
       </c>
       <c r="I50" s="1">
         <v>0</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="K50" s="1" t="s">
         <v>394</v>
@@ -18308,28 +18546,28 @@
     </row>
     <row r="51" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C51" s="1">
-        <v>43009</v>
+        <v>43008</v>
       </c>
       <c r="D51" s="1">
         <v>6</v>
       </c>
       <c r="E51" s="1">
-        <v>300</v>
+        <v>50</v>
       </c>
       <c r="F51" s="1">
-        <v>500</v>
+        <v>10</v>
       </c>
       <c r="G51" s="1">
         <v>3</v>
       </c>
       <c r="H51" s="3">
-        <v>3009</v>
+        <v>3008</v>
       </c>
       <c r="I51" s="1">
         <v>0</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="K51" s="1" t="s">
         <v>394</v>
@@ -18349,28 +18587,28 @@
     </row>
     <row r="52" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C52" s="1">
-        <v>43010</v>
+        <v>43009</v>
       </c>
       <c r="D52" s="1">
         <v>6</v>
       </c>
       <c r="E52" s="1">
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="F52" s="1">
-        <v>5</v>
+        <v>500</v>
       </c>
       <c r="G52" s="1">
         <v>3</v>
       </c>
       <c r="H52" s="3">
-        <v>3010</v>
+        <v>3009</v>
       </c>
       <c r="I52" s="1">
         <v>0</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="K52" s="1" t="s">
         <v>394</v>
@@ -18390,13 +18628,13 @@
     </row>
     <row r="53" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C53" s="1">
-        <v>43011</v>
+        <v>43010</v>
       </c>
       <c r="D53" s="1">
         <v>6</v>
       </c>
       <c r="E53" s="1">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F53" s="1">
         <v>5</v>
@@ -18405,13 +18643,13 @@
         <v>3</v>
       </c>
       <c r="H53" s="3">
-        <v>3011</v>
+        <v>3010</v>
       </c>
       <c r="I53" s="1">
         <v>0</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="K53" s="1" t="s">
         <v>394</v>
@@ -18431,13 +18669,13 @@
     </row>
     <row r="54" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C54" s="1">
-        <v>43012</v>
+        <v>43011</v>
       </c>
       <c r="D54" s="1">
         <v>6</v>
       </c>
       <c r="E54" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F54" s="1">
         <v>5</v>
@@ -18446,22 +18684,22 @@
         <v>3</v>
       </c>
       <c r="H54" s="3">
-        <v>3012</v>
+        <v>3011</v>
       </c>
       <c r="I54" s="1">
         <v>0</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>341</v>
+        <v>394</v>
       </c>
       <c r="L54" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M54" s="1">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="N54" s="1">
         <v>10</v>
@@ -18470,60 +18708,57 @@
         <v>10</v>
       </c>
     </row>
-    <row r="55" customFormat="1" customHeight="1"/>
-    <row r="56" s="1" customFormat="1" customHeight="1" spans="3:16">
-      <c r="C56" s="1">
-        <v>43102</v>
-      </c>
-      <c r="D56" s="1">
+    <row r="55" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C55" s="1">
+        <v>43012</v>
+      </c>
+      <c r="D55" s="1">
         <v>6</v>
       </c>
-      <c r="E56" s="1">
-        <v>50</v>
-      </c>
-      <c r="F56" s="1">
+      <c r="E55" s="1">
+        <v>10</v>
+      </c>
+      <c r="F55" s="1">
         <v>5</v>
       </c>
-      <c r="G56" s="1">
+      <c r="G55" s="1">
         <v>3</v>
       </c>
-      <c r="H56" s="3">
-        <v>3002</v>
-      </c>
-      <c r="I56" s="1">
-        <v>0</v>
-      </c>
-      <c r="J56" s="3" t="s">
-        <v>437</v>
-      </c>
-      <c r="K56" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="L56" s="1">
+      <c r="H55" s="3">
+        <v>3012</v>
+      </c>
+      <c r="I55" s="1">
+        <v>0</v>
+      </c>
+      <c r="J55" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="K55" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="L55" s="1">
         <v>4</v>
       </c>
-      <c r="M56" s="1">
-        <v>0</v>
-      </c>
-      <c r="N56" s="1">
+      <c r="M55" s="1">
+        <v>15</v>
+      </c>
+      <c r="N55" s="1">
         <v>10</v>
       </c>
-      <c r="O56" s="1">
+      <c r="O55" s="1">
         <v>10</v>
       </c>
-      <c r="P56" s="1">
-        <v>25</v>
-      </c>
-    </row>
+    </row>
+    <row r="56" customFormat="1" customHeight="1"/>
     <row r="57" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C57" s="1">
-        <v>43112</v>
+        <v>43102</v>
       </c>
       <c r="D57" s="1">
         <v>6</v>
       </c>
       <c r="E57" s="1">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="F57" s="1">
         <v>5</v>
@@ -18532,16 +18767,16 @@
         <v>3</v>
       </c>
       <c r="H57" s="3">
-        <v>3012</v>
+        <v>3002</v>
       </c>
       <c r="I57" s="1">
         <v>0</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>439</v>
+        <v>407</v>
       </c>
       <c r="L57" s="1">
         <v>4</v>
@@ -18560,9 +18795,2136 @@
       </c>
     </row>
     <row r="58" s="1" customFormat="1" customHeight="1" spans="3:16">
-      <c r="H58" s="3"/>
-      <c r="I58" s="1"/>
-      <c r="J58" s="3"/>
+      <c r="C58" s="1">
+        <v>43112</v>
+      </c>
+      <c r="D58" s="1">
+        <v>6</v>
+      </c>
+      <c r="E58" s="1">
+        <v>10</v>
+      </c>
+      <c r="F58" s="1">
+        <v>5</v>
+      </c>
+      <c r="G58" s="1">
+        <v>3</v>
+      </c>
+      <c r="H58" s="3">
+        <v>3012</v>
+      </c>
+      <c r="I58" s="1">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="K58" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="L58" s="1">
+        <v>4</v>
+      </c>
+      <c r="M58" s="1">
+        <v>0</v>
+      </c>
+      <c r="N58" s="1">
+        <v>10</v>
+      </c>
+      <c r="O58" s="1">
+        <v>10</v>
+      </c>
+      <c r="P58" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="59" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="H59" s="3"/>
+      <c r="I59" s="1"/>
+      <c r="J59" s="3"/>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="S3:S5 C3:L5" errorStyle="warning">
+      <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="C3:U59"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
+  <cols>
+    <col min="1" max="4" width="9" style="1"/>
+    <col min="5" max="7" width="10.875" style="1" customWidth="1"/>
+    <col min="8" max="9" width="9" style="1"/>
+    <col min="10" max="10" width="15.625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="25.625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="17.375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="13.25" style="1" customWidth="1"/>
+    <col min="14" max="14" width="12.25" style="1" customWidth="1"/>
+    <col min="15" max="15" width="13.75" style="1" customWidth="1"/>
+    <col min="16" max="16" width="10.625" style="1" customWidth="1"/>
+    <col min="17" max="17" width="9.16666666666667" style="1" customWidth="1"/>
+    <col min="18" max="18" width="8.58333333333333" style="1" customWidth="1"/>
+    <col min="19" max="19" width="7.375" style="1" customWidth="1"/>
+    <col min="20" max="20" width="9.25" style="1" customWidth="1"/>
+    <col min="21" max="21" width="9.66666666666667" style="1" customWidth="1"/>
+    <col min="22" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:21">
+      <c r="C3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:21">
+      <c r="C4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="R4" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="S4" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="T4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="U4" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:21">
+      <c r="C5" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q5" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="R5" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="S5" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="T5" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="U5" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:21">
+      <c r="C6" s="1">
+        <v>51001</v>
+      </c>
+      <c r="D6" s="1">
+        <v>7</v>
+      </c>
+      <c r="E6" s="1">
+        <v>300</v>
+      </c>
+      <c r="F6" s="1">
+        <v>500</v>
+      </c>
+      <c r="G6" s="1">
+        <v>1</v>
+      </c>
+      <c r="H6" s="3">
+        <v>1001</v>
+      </c>
+      <c r="I6" s="1">
+        <v>0</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="L6" s="1">
+        <v>6</v>
+      </c>
+      <c r="M6" s="1">
+        <v>40</v>
+      </c>
+      <c r="N6" s="1">
+        <v>11</v>
+      </c>
+      <c r="O6" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:21">
+      <c r="C7" s="1">
+        <v>51002</v>
+      </c>
+      <c r="D7" s="1">
+        <v>7</v>
+      </c>
+      <c r="E7" s="1">
+        <v>100</v>
+      </c>
+      <c r="F7" s="1">
+        <v>25</v>
+      </c>
+      <c r="G7" s="1">
+        <v>1</v>
+      </c>
+      <c r="H7" s="3">
+        <v>1002</v>
+      </c>
+      <c r="I7" s="1">
+        <v>0</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="L7" s="1">
+        <v>6</v>
+      </c>
+      <c r="M7" s="1">
+        <v>40</v>
+      </c>
+      <c r="N7" s="1">
+        <v>11</v>
+      </c>
+      <c r="O7" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:21">
+      <c r="C8" s="1">
+        <v>51003</v>
+      </c>
+      <c r="D8" s="1">
+        <v>7</v>
+      </c>
+      <c r="E8" s="1">
+        <v>300</v>
+      </c>
+      <c r="F8" s="1">
+        <v>500</v>
+      </c>
+      <c r="G8" s="1">
+        <v>1</v>
+      </c>
+      <c r="H8" s="3">
+        <v>1003</v>
+      </c>
+      <c r="I8" s="1">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="L8" s="1">
+        <v>6</v>
+      </c>
+      <c r="M8" s="1">
+        <v>40</v>
+      </c>
+      <c r="N8" s="1">
+        <v>11</v>
+      </c>
+      <c r="O8" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:21">
+      <c r="C9" s="1">
+        <v>51004</v>
+      </c>
+      <c r="D9" s="1">
+        <v>7</v>
+      </c>
+      <c r="E9" s="1">
+        <v>300</v>
+      </c>
+      <c r="F9" s="1">
+        <v>500</v>
+      </c>
+      <c r="G9" s="1">
+        <v>1</v>
+      </c>
+      <c r="H9" s="3">
+        <v>1004</v>
+      </c>
+      <c r="I9" s="1">
+        <v>0</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="L9" s="1">
+        <v>6</v>
+      </c>
+      <c r="M9" s="1">
+        <v>40</v>
+      </c>
+      <c r="N9" s="1">
+        <v>11</v>
+      </c>
+      <c r="O9" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:21">
+      <c r="C10" s="1">
+        <v>51005</v>
+      </c>
+      <c r="D10" s="1">
+        <v>7</v>
+      </c>
+      <c r="E10" s="1">
+        <v>100</v>
+      </c>
+      <c r="F10" s="1">
+        <v>25</v>
+      </c>
+      <c r="G10" s="1">
+        <v>1</v>
+      </c>
+      <c r="H10" s="3">
+        <v>1005</v>
+      </c>
+      <c r="I10" s="1">
+        <v>0</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="L10" s="1">
+        <v>6</v>
+      </c>
+      <c r="M10" s="1">
+        <v>40</v>
+      </c>
+      <c r="N10" s="1">
+        <v>11</v>
+      </c>
+      <c r="O10" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:21">
+      <c r="C11" s="1">
+        <v>51006</v>
+      </c>
+      <c r="D11" s="1">
+        <v>7</v>
+      </c>
+      <c r="E11" s="1">
+        <v>150</v>
+      </c>
+      <c r="F11" s="1">
+        <v>25</v>
+      </c>
+      <c r="G11" s="1">
+        <v>1</v>
+      </c>
+      <c r="H11" s="3">
+        <v>1006</v>
+      </c>
+      <c r="I11" s="1">
+        <v>0</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="L11" s="1">
+        <v>6</v>
+      </c>
+      <c r="M11" s="1">
+        <v>40</v>
+      </c>
+      <c r="N11" s="1">
+        <v>11</v>
+      </c>
+      <c r="O11" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:21">
+      <c r="C12" s="1">
+        <v>51007</v>
+      </c>
+      <c r="D12" s="1">
+        <v>7</v>
+      </c>
+      <c r="E12" s="1">
+        <v>300</v>
+      </c>
+      <c r="F12" s="1">
+        <v>500</v>
+      </c>
+      <c r="G12" s="1">
+        <v>1</v>
+      </c>
+      <c r="H12" s="3">
+        <v>1007</v>
+      </c>
+      <c r="I12" s="1">
+        <v>0</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="L12" s="1">
+        <v>6</v>
+      </c>
+      <c r="M12" s="1">
+        <v>40</v>
+      </c>
+      <c r="N12" s="1">
+        <v>11</v>
+      </c>
+      <c r="O12" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:21">
+      <c r="C13" s="1">
+        <v>51008</v>
+      </c>
+      <c r="D13" s="1">
+        <v>7</v>
+      </c>
+      <c r="E13" s="1">
+        <v>100</v>
+      </c>
+      <c r="F13" s="1">
+        <v>10</v>
+      </c>
+      <c r="G13" s="1">
+        <v>1</v>
+      </c>
+      <c r="H13" s="3">
+        <v>1008</v>
+      </c>
+      <c r="I13" s="1">
+        <v>0</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="L13" s="1">
+        <v>6</v>
+      </c>
+      <c r="M13" s="1">
+        <v>40</v>
+      </c>
+      <c r="N13" s="1">
+        <v>11</v>
+      </c>
+      <c r="O13" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:21">
+      <c r="C14" s="1">
+        <v>51009</v>
+      </c>
+      <c r="D14" s="1">
+        <v>7</v>
+      </c>
+      <c r="E14" s="1">
+        <v>300</v>
+      </c>
+      <c r="F14" s="1">
+        <v>500</v>
+      </c>
+      <c r="G14" s="1">
+        <v>1</v>
+      </c>
+      <c r="H14" s="3">
+        <v>1009</v>
+      </c>
+      <c r="I14" s="1">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="L14" s="1">
+        <v>6</v>
+      </c>
+      <c r="M14" s="1">
+        <v>40</v>
+      </c>
+      <c r="N14" s="1">
+        <v>11</v>
+      </c>
+      <c r="O14" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:21">
+      <c r="C15" s="1">
+        <v>51010</v>
+      </c>
+      <c r="D15" s="1">
+        <v>7</v>
+      </c>
+      <c r="E15" s="1">
+        <v>30</v>
+      </c>
+      <c r="F15" s="1">
+        <v>5</v>
+      </c>
+      <c r="G15" s="1">
+        <v>1</v>
+      </c>
+      <c r="H15" s="3">
+        <v>1010</v>
+      </c>
+      <c r="I15" s="1">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="L15" s="1">
+        <v>6</v>
+      </c>
+      <c r="M15" s="1">
+        <v>40</v>
+      </c>
+      <c r="N15" s="1">
+        <v>11</v>
+      </c>
+      <c r="O15" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:21">
+      <c r="C16" s="1">
+        <v>51011</v>
+      </c>
+      <c r="D16" s="1">
+        <v>7</v>
+      </c>
+      <c r="E16" s="1">
+        <v>20</v>
+      </c>
+      <c r="F16" s="1">
+        <v>5</v>
+      </c>
+      <c r="G16" s="1">
+        <v>1</v>
+      </c>
+      <c r="H16" s="3">
+        <v>1011</v>
+      </c>
+      <c r="I16" s="1">
+        <v>0</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="L16" s="1">
+        <v>6</v>
+      </c>
+      <c r="M16" s="1">
+        <v>40</v>
+      </c>
+      <c r="N16" s="1">
+        <v>11</v>
+      </c>
+      <c r="O16" s="1">
+        <v>11</v>
+      </c>
+      <c r="T16" s="4"/>
+    </row>
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:20">
+      <c r="C17" s="1">
+        <v>51012</v>
+      </c>
+      <c r="D17" s="1">
+        <v>7</v>
+      </c>
+      <c r="E17" s="1">
+        <v>10</v>
+      </c>
+      <c r="F17" s="1">
+        <v>5</v>
+      </c>
+      <c r="G17" s="1">
+        <v>1</v>
+      </c>
+      <c r="H17" s="3">
+        <v>1012</v>
+      </c>
+      <c r="I17" s="1">
+        <v>0</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="L17" s="1">
+        <v>4</v>
+      </c>
+      <c r="M17" s="1">
+        <v>30</v>
+      </c>
+      <c r="N17" s="1">
+        <v>11</v>
+      </c>
+      <c r="O17" s="1">
+        <v>11</v>
+      </c>
+      <c r="T17" s="4"/>
+    </row>
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:20">
+      <c r="H18" s="3"/>
+      <c r="J18" s="3"/>
+      <c r="T18" s="4"/>
+    </row>
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:20">
+      <c r="C19" s="1">
+        <v>51102</v>
+      </c>
+      <c r="D19" s="1">
+        <v>7</v>
+      </c>
+      <c r="E19" s="1">
+        <v>50</v>
+      </c>
+      <c r="F19" s="1">
+        <v>5</v>
+      </c>
+      <c r="G19" s="1">
+        <v>1</v>
+      </c>
+      <c r="H19" s="3">
+        <v>1002</v>
+      </c>
+      <c r="I19" s="1">
+        <v>0</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="L19" s="1">
+        <v>4</v>
+      </c>
+      <c r="M19" s="1">
+        <v>0</v>
+      </c>
+      <c r="N19" s="1">
+        <v>11</v>
+      </c>
+      <c r="O19" s="1">
+        <v>11</v>
+      </c>
+      <c r="P19" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:20">
+      <c r="C20" s="1">
+        <v>51110</v>
+      </c>
+      <c r="D20" s="1">
+        <v>7</v>
+      </c>
+      <c r="E20" s="1">
+        <v>20</v>
+      </c>
+      <c r="F20" s="1">
+        <v>5</v>
+      </c>
+      <c r="G20" s="1">
+        <v>1</v>
+      </c>
+      <c r="H20" s="3">
+        <v>1010</v>
+      </c>
+      <c r="I20" s="1">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="L20" s="1">
+        <v>4</v>
+      </c>
+      <c r="M20" s="1">
+        <v>0</v>
+      </c>
+      <c r="N20" s="1">
+        <v>11</v>
+      </c>
+      <c r="O20" s="1">
+        <v>11</v>
+      </c>
+      <c r="P20" s="1">
+        <v>40</v>
+      </c>
+      <c r="T20" s="4"/>
+    </row>
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:20">
+      <c r="C21" s="1">
+        <v>51112</v>
+      </c>
+      <c r="D21" s="1">
+        <v>7</v>
+      </c>
+      <c r="E21" s="1">
+        <v>10</v>
+      </c>
+      <c r="F21" s="1">
+        <v>5</v>
+      </c>
+      <c r="G21" s="1">
+        <v>1</v>
+      </c>
+      <c r="H21" s="3">
+        <v>1012</v>
+      </c>
+      <c r="I21" s="1">
+        <v>0</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="L21" s="1">
+        <v>4</v>
+      </c>
+      <c r="M21" s="1">
+        <v>0</v>
+      </c>
+      <c r="N21" s="1">
+        <v>11</v>
+      </c>
+      <c r="O21" s="1">
+        <v>11</v>
+      </c>
+      <c r="P21" s="1">
+        <v>40</v>
+      </c>
+      <c r="T21" s="4"/>
+    </row>
+    <row r="22" s="1" customFormat="1" customHeight="1" spans="3:20">
+      <c r="H22" s="3"/>
+      <c r="J22" s="3"/>
+      <c r="T22" s="4"/>
+    </row>
+    <row r="23" s="1" customFormat="1" customHeight="1" spans="3:20">
+      <c r="H23" s="3"/>
+      <c r="J23" s="3"/>
+      <c r="T23" s="4"/>
+    </row>
+    <row r="24" s="1" customFormat="1" customHeight="1" spans="3:20">
+      <c r="H24" s="3"/>
+      <c r="J24" s="3"/>
+      <c r="T24" s="4"/>
+    </row>
+    <row r="25" s="1" customFormat="1" customHeight="1" spans="3:20">
+      <c r="H25" s="3"/>
+      <c r="J25" s="3"/>
+      <c r="T25" s="4"/>
+    </row>
+    <row r="26" s="1" customFormat="1" customHeight="1" spans="3:20">
+      <c r="C26" s="1">
+        <v>52001</v>
+      </c>
+      <c r="D26" s="1">
+        <v>7</v>
+      </c>
+      <c r="E26" s="1">
+        <v>300</v>
+      </c>
+      <c r="F26" s="1">
+        <v>500</v>
+      </c>
+      <c r="G26" s="1">
+        <v>2</v>
+      </c>
+      <c r="H26" s="3">
+        <v>2001</v>
+      </c>
+      <c r="I26" s="1">
+        <v>0</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="L26" s="1">
+        <v>6</v>
+      </c>
+      <c r="M26" s="1">
+        <v>40</v>
+      </c>
+      <c r="N26" s="1">
+        <v>11</v>
+      </c>
+      <c r="O26" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:20">
+      <c r="C27" s="1">
+        <v>52002</v>
+      </c>
+      <c r="D27" s="1">
+        <v>7</v>
+      </c>
+      <c r="E27" s="1">
+        <v>100</v>
+      </c>
+      <c r="F27" s="1">
+        <v>25</v>
+      </c>
+      <c r="G27" s="1">
+        <v>2</v>
+      </c>
+      <c r="H27" s="3">
+        <v>2002</v>
+      </c>
+      <c r="I27" s="1">
+        <v>0</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="L27" s="1">
+        <v>6</v>
+      </c>
+      <c r="M27" s="1">
+        <v>40</v>
+      </c>
+      <c r="N27" s="1">
+        <v>11</v>
+      </c>
+      <c r="O27" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28" s="1" customFormat="1" customHeight="1" spans="3:20">
+      <c r="C28" s="1">
+        <v>52003</v>
+      </c>
+      <c r="D28" s="1">
+        <v>7</v>
+      </c>
+      <c r="E28" s="1">
+        <v>300</v>
+      </c>
+      <c r="F28" s="1">
+        <v>500</v>
+      </c>
+      <c r="G28" s="1">
+        <v>2</v>
+      </c>
+      <c r="H28" s="3">
+        <v>2003</v>
+      </c>
+      <c r="I28" s="1">
+        <v>0</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="L28" s="1">
+        <v>6</v>
+      </c>
+      <c r="M28" s="1">
+        <v>40</v>
+      </c>
+      <c r="N28" s="1">
+        <v>11</v>
+      </c>
+      <c r="O28" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="29" s="1" customFormat="1" customHeight="1" spans="3:20">
+      <c r="C29" s="1">
+        <v>52004</v>
+      </c>
+      <c r="D29" s="1">
+        <v>7</v>
+      </c>
+      <c r="E29" s="1">
+        <v>300</v>
+      </c>
+      <c r="F29" s="1">
+        <v>500</v>
+      </c>
+      <c r="G29" s="1">
+        <v>2</v>
+      </c>
+      <c r="H29" s="3">
+        <v>2004</v>
+      </c>
+      <c r="I29" s="1">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="L29" s="1">
+        <v>6</v>
+      </c>
+      <c r="M29" s="1">
+        <v>40</v>
+      </c>
+      <c r="N29" s="1">
+        <v>11</v>
+      </c>
+      <c r="O29" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30" s="1" customFormat="1" customHeight="1" spans="3:20">
+      <c r="C30" s="1">
+        <v>52005</v>
+      </c>
+      <c r="D30" s="1">
+        <v>7</v>
+      </c>
+      <c r="E30" s="1">
+        <v>100</v>
+      </c>
+      <c r="F30" s="1">
+        <v>25</v>
+      </c>
+      <c r="G30" s="1">
+        <v>2</v>
+      </c>
+      <c r="H30" s="3">
+        <v>2005</v>
+      </c>
+      <c r="I30" s="1">
+        <v>0</v>
+      </c>
+      <c r="J30" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="L30" s="1">
+        <v>6</v>
+      </c>
+      <c r="M30" s="1">
+        <v>40</v>
+      </c>
+      <c r="N30" s="1">
+        <v>11</v>
+      </c>
+      <c r="O30" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="31" s="1" customFormat="1" customHeight="1" spans="3:20">
+      <c r="C31" s="1">
+        <v>52006</v>
+      </c>
+      <c r="D31" s="1">
+        <v>7</v>
+      </c>
+      <c r="E31" s="1">
+        <v>150</v>
+      </c>
+      <c r="F31" s="1">
+        <v>25</v>
+      </c>
+      <c r="G31" s="1">
+        <v>2</v>
+      </c>
+      <c r="H31" s="3">
+        <v>2006</v>
+      </c>
+      <c r="I31" s="1">
+        <v>0</v>
+      </c>
+      <c r="J31" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="L31" s="1">
+        <v>6</v>
+      </c>
+      <c r="M31" s="1">
+        <v>40</v>
+      </c>
+      <c r="N31" s="1">
+        <v>11</v>
+      </c>
+      <c r="O31" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="32" s="1" customFormat="1" customHeight="1" spans="3:20">
+      <c r="C32" s="1">
+        <v>52007</v>
+      </c>
+      <c r="D32" s="1">
+        <v>7</v>
+      </c>
+      <c r="E32" s="1">
+        <v>300</v>
+      </c>
+      <c r="F32" s="1">
+        <v>500</v>
+      </c>
+      <c r="G32" s="1">
+        <v>2</v>
+      </c>
+      <c r="H32" s="3">
+        <v>2007</v>
+      </c>
+      <c r="I32" s="1">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="L32" s="1">
+        <v>6</v>
+      </c>
+      <c r="M32" s="1">
+        <v>40</v>
+      </c>
+      <c r="N32" s="1">
+        <v>11</v>
+      </c>
+      <c r="O32" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="33" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="C33" s="1">
+        <v>52008</v>
+      </c>
+      <c r="D33" s="1">
+        <v>7</v>
+      </c>
+      <c r="E33" s="1">
+        <v>100</v>
+      </c>
+      <c r="F33" s="1">
+        <v>10</v>
+      </c>
+      <c r="G33" s="1">
+        <v>2</v>
+      </c>
+      <c r="H33" s="3">
+        <v>2008</v>
+      </c>
+      <c r="I33" s="1">
+        <v>0</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="L33" s="1">
+        <v>6</v>
+      </c>
+      <c r="M33" s="1">
+        <v>40</v>
+      </c>
+      <c r="N33" s="1">
+        <v>11</v>
+      </c>
+      <c r="O33" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="34" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="C34" s="1">
+        <v>52009</v>
+      </c>
+      <c r="D34" s="1">
+        <v>7</v>
+      </c>
+      <c r="E34" s="1">
+        <v>300</v>
+      </c>
+      <c r="F34" s="1">
+        <v>500</v>
+      </c>
+      <c r="G34" s="1">
+        <v>2</v>
+      </c>
+      <c r="H34" s="3">
+        <v>2009</v>
+      </c>
+      <c r="I34" s="1">
+        <v>0</v>
+      </c>
+      <c r="J34" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="L34" s="1">
+        <v>6</v>
+      </c>
+      <c r="M34" s="1">
+        <v>40</v>
+      </c>
+      <c r="N34" s="1">
+        <v>11</v>
+      </c>
+      <c r="O34" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="35" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="C35" s="1">
+        <v>52010</v>
+      </c>
+      <c r="D35" s="1">
+        <v>7</v>
+      </c>
+      <c r="E35" s="1">
+        <v>30</v>
+      </c>
+      <c r="F35" s="1">
+        <v>5</v>
+      </c>
+      <c r="G35" s="1">
+        <v>2</v>
+      </c>
+      <c r="H35" s="3">
+        <v>2010</v>
+      </c>
+      <c r="I35" s="1">
+        <v>0</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="L35" s="1">
+        <v>6</v>
+      </c>
+      <c r="M35" s="1">
+        <v>40</v>
+      </c>
+      <c r="N35" s="1">
+        <v>11</v>
+      </c>
+      <c r="O35" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="36" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="C36" s="1">
+        <v>52011</v>
+      </c>
+      <c r="D36" s="1">
+        <v>7</v>
+      </c>
+      <c r="E36" s="1">
+        <v>20</v>
+      </c>
+      <c r="F36" s="1">
+        <v>5</v>
+      </c>
+      <c r="G36" s="1">
+        <v>2</v>
+      </c>
+      <c r="H36" s="3">
+        <v>2011</v>
+      </c>
+      <c r="I36" s="1">
+        <v>0</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="L36" s="1">
+        <v>6</v>
+      </c>
+      <c r="M36" s="1">
+        <v>40</v>
+      </c>
+      <c r="N36" s="1">
+        <v>11</v>
+      </c>
+      <c r="O36" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="37" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="C37" s="1">
+        <v>52012</v>
+      </c>
+      <c r="D37" s="1">
+        <v>7</v>
+      </c>
+      <c r="E37" s="1">
+        <v>10</v>
+      </c>
+      <c r="F37" s="1">
+        <v>5</v>
+      </c>
+      <c r="G37" s="1">
+        <v>2</v>
+      </c>
+      <c r="H37" s="3">
+        <v>2012</v>
+      </c>
+      <c r="I37" s="1">
+        <v>0</v>
+      </c>
+      <c r="J37" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="K37" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="L37" s="1">
+        <v>4</v>
+      </c>
+      <c r="M37" s="1">
+        <v>30</v>
+      </c>
+      <c r="N37" s="1">
+        <v>11</v>
+      </c>
+      <c r="O37" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="38" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="H38" s="3"/>
+      <c r="J38" s="3"/>
+    </row>
+    <row r="39" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="C39" s="1">
+        <v>52102</v>
+      </c>
+      <c r="D39" s="1">
+        <v>7</v>
+      </c>
+      <c r="E39" s="1">
+        <v>50</v>
+      </c>
+      <c r="F39" s="1">
+        <v>5</v>
+      </c>
+      <c r="G39" s="1">
+        <v>2</v>
+      </c>
+      <c r="H39" s="3">
+        <v>2002</v>
+      </c>
+      <c r="I39" s="1">
+        <v>0</v>
+      </c>
+      <c r="J39" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="K39" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="L39" s="1">
+        <v>4</v>
+      </c>
+      <c r="M39" s="1">
+        <v>0</v>
+      </c>
+      <c r="N39" s="1">
+        <v>11</v>
+      </c>
+      <c r="O39" s="1">
+        <v>11</v>
+      </c>
+      <c r="P39" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="40" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="C40" s="1">
+        <v>52107</v>
+      </c>
+      <c r="D40" s="1">
+        <v>7</v>
+      </c>
+      <c r="E40" s="1">
+        <v>50</v>
+      </c>
+      <c r="F40" s="1">
+        <v>5</v>
+      </c>
+      <c r="G40" s="1">
+        <v>2</v>
+      </c>
+      <c r="H40" s="3">
+        <v>2007</v>
+      </c>
+      <c r="I40" s="1">
+        <v>0</v>
+      </c>
+      <c r="J40" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="K40" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="L40" s="1">
+        <v>4</v>
+      </c>
+      <c r="M40" s="1">
+        <v>0</v>
+      </c>
+      <c r="N40" s="1">
+        <v>11</v>
+      </c>
+      <c r="O40" s="1">
+        <v>11</v>
+      </c>
+      <c r="P40" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="41" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="C41" s="1">
+        <v>52112</v>
+      </c>
+      <c r="D41" s="1">
+        <v>7</v>
+      </c>
+      <c r="E41" s="1">
+        <v>10</v>
+      </c>
+      <c r="F41" s="1">
+        <v>5</v>
+      </c>
+      <c r="G41" s="1">
+        <v>2</v>
+      </c>
+      <c r="H41" s="3">
+        <v>2012</v>
+      </c>
+      <c r="I41" s="1">
+        <v>0</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="K41" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="L41" s="1">
+        <v>4</v>
+      </c>
+      <c r="M41" s="1">
+        <v>0</v>
+      </c>
+      <c r="N41" s="1">
+        <v>11</v>
+      </c>
+      <c r="O41" s="1">
+        <v>11</v>
+      </c>
+      <c r="R41" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="43" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="H43" s="3"/>
+      <c r="J43" s="3"/>
+    </row>
+    <row r="44" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="C44" s="1">
+        <v>53001</v>
+      </c>
+      <c r="D44" s="1">
+        <v>7</v>
+      </c>
+      <c r="E44" s="1">
+        <v>300</v>
+      </c>
+      <c r="F44" s="1">
+        <v>500</v>
+      </c>
+      <c r="G44" s="1">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3">
+        <v>3001</v>
+      </c>
+      <c r="I44" s="1">
+        <v>0</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="K44" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="L44" s="1">
+        <v>6</v>
+      </c>
+      <c r="M44" s="1">
+        <v>40</v>
+      </c>
+      <c r="N44" s="1">
+        <v>11</v>
+      </c>
+      <c r="O44" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="45" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="C45" s="1">
+        <v>53002</v>
+      </c>
+      <c r="D45" s="1">
+        <v>7</v>
+      </c>
+      <c r="E45" s="1">
+        <v>100</v>
+      </c>
+      <c r="F45" s="1">
+        <v>25</v>
+      </c>
+      <c r="G45" s="1">
+        <v>3</v>
+      </c>
+      <c r="H45" s="3">
+        <v>3002</v>
+      </c>
+      <c r="I45" s="1">
+        <v>0</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="K45" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="L45" s="1">
+        <v>6</v>
+      </c>
+      <c r="M45" s="1">
+        <v>40</v>
+      </c>
+      <c r="N45" s="1">
+        <v>11</v>
+      </c>
+      <c r="O45" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="46" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="C46" s="1">
+        <v>53003</v>
+      </c>
+      <c r="D46" s="1">
+        <v>7</v>
+      </c>
+      <c r="E46" s="1">
+        <v>300</v>
+      </c>
+      <c r="F46" s="1">
+        <v>500</v>
+      </c>
+      <c r="G46" s="1">
+        <v>3</v>
+      </c>
+      <c r="H46" s="3">
+        <v>3003</v>
+      </c>
+      <c r="I46" s="1">
+        <v>0</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="K46" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="L46" s="1">
+        <v>6</v>
+      </c>
+      <c r="M46" s="1">
+        <v>40</v>
+      </c>
+      <c r="N46" s="1">
+        <v>11</v>
+      </c>
+      <c r="O46" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="47" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="C47" s="1">
+        <v>53004</v>
+      </c>
+      <c r="D47" s="1">
+        <v>7</v>
+      </c>
+      <c r="E47" s="1">
+        <v>300</v>
+      </c>
+      <c r="F47" s="1">
+        <v>500</v>
+      </c>
+      <c r="G47" s="1">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3">
+        <v>3004</v>
+      </c>
+      <c r="I47" s="1">
+        <v>0</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="K47" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="L47" s="1">
+        <v>6</v>
+      </c>
+      <c r="M47" s="1">
+        <v>40</v>
+      </c>
+      <c r="N47" s="1">
+        <v>11</v>
+      </c>
+      <c r="O47" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="48" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="C48" s="1">
+        <v>53005</v>
+      </c>
+      <c r="D48" s="1">
+        <v>7</v>
+      </c>
+      <c r="E48" s="1">
+        <v>100</v>
+      </c>
+      <c r="F48" s="1">
+        <v>25</v>
+      </c>
+      <c r="G48" s="1">
+        <v>3</v>
+      </c>
+      <c r="H48" s="3">
+        <v>3005</v>
+      </c>
+      <c r="I48" s="1">
+        <v>0</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="K48" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="L48" s="1">
+        <v>6</v>
+      </c>
+      <c r="M48" s="1">
+        <v>40</v>
+      </c>
+      <c r="N48" s="1">
+        <v>11</v>
+      </c>
+      <c r="O48" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="49" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C49" s="1">
+        <v>53006</v>
+      </c>
+      <c r="D49" s="1">
+        <v>7</v>
+      </c>
+      <c r="E49" s="1">
+        <v>150</v>
+      </c>
+      <c r="F49" s="1">
+        <v>25</v>
+      </c>
+      <c r="G49" s="1">
+        <v>3</v>
+      </c>
+      <c r="H49" s="3">
+        <v>3006</v>
+      </c>
+      <c r="I49" s="1">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="K49" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="L49" s="1">
+        <v>6</v>
+      </c>
+      <c r="M49" s="1">
+        <v>40</v>
+      </c>
+      <c r="N49" s="1">
+        <v>11</v>
+      </c>
+      <c r="O49" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="50" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C50" s="1">
+        <v>53007</v>
+      </c>
+      <c r="D50" s="1">
+        <v>7</v>
+      </c>
+      <c r="E50" s="1">
+        <v>300</v>
+      </c>
+      <c r="F50" s="1">
+        <v>500</v>
+      </c>
+      <c r="G50" s="1">
+        <v>3</v>
+      </c>
+      <c r="H50" s="3">
+        <v>3007</v>
+      </c>
+      <c r="I50" s="1">
+        <v>0</v>
+      </c>
+      <c r="J50" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="K50" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="L50" s="1">
+        <v>6</v>
+      </c>
+      <c r="M50" s="1">
+        <v>40</v>
+      </c>
+      <c r="N50" s="1">
+        <v>11</v>
+      </c>
+      <c r="O50" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="51" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C51" s="1">
+        <v>53008</v>
+      </c>
+      <c r="D51" s="1">
+        <v>7</v>
+      </c>
+      <c r="E51" s="1">
+        <v>50</v>
+      </c>
+      <c r="F51" s="1">
+        <v>10</v>
+      </c>
+      <c r="G51" s="1">
+        <v>3</v>
+      </c>
+      <c r="H51" s="3">
+        <v>3008</v>
+      </c>
+      <c r="I51" s="1">
+        <v>0</v>
+      </c>
+      <c r="J51" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="K51" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="L51" s="1">
+        <v>6</v>
+      </c>
+      <c r="M51" s="1">
+        <v>40</v>
+      </c>
+      <c r="N51" s="1">
+        <v>11</v>
+      </c>
+      <c r="O51" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="52" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C52" s="1">
+        <v>53009</v>
+      </c>
+      <c r="D52" s="1">
+        <v>7</v>
+      </c>
+      <c r="E52" s="1">
+        <v>300</v>
+      </c>
+      <c r="F52" s="1">
+        <v>500</v>
+      </c>
+      <c r="G52" s="1">
+        <v>3</v>
+      </c>
+      <c r="H52" s="3">
+        <v>3009</v>
+      </c>
+      <c r="I52" s="1">
+        <v>0</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="K52" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="L52" s="1">
+        <v>6</v>
+      </c>
+      <c r="M52" s="1">
+        <v>40</v>
+      </c>
+      <c r="N52" s="1">
+        <v>11</v>
+      </c>
+      <c r="O52" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="53" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C53" s="1">
+        <v>53010</v>
+      </c>
+      <c r="D53" s="1">
+        <v>7</v>
+      </c>
+      <c r="E53" s="1">
+        <v>30</v>
+      </c>
+      <c r="F53" s="1">
+        <v>5</v>
+      </c>
+      <c r="G53" s="1">
+        <v>3</v>
+      </c>
+      <c r="H53" s="3">
+        <v>3010</v>
+      </c>
+      <c r="I53" s="1">
+        <v>0</v>
+      </c>
+      <c r="J53" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="K53" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="L53" s="1">
+        <v>6</v>
+      </c>
+      <c r="M53" s="1">
+        <v>40</v>
+      </c>
+      <c r="N53" s="1">
+        <v>11</v>
+      </c>
+      <c r="O53" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="54" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C54" s="1">
+        <v>53011</v>
+      </c>
+      <c r="D54" s="1">
+        <v>7</v>
+      </c>
+      <c r="E54" s="1">
+        <v>20</v>
+      </c>
+      <c r="F54" s="1">
+        <v>5</v>
+      </c>
+      <c r="G54" s="1">
+        <v>3</v>
+      </c>
+      <c r="H54" s="3">
+        <v>3011</v>
+      </c>
+      <c r="I54" s="1">
+        <v>0</v>
+      </c>
+      <c r="J54" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="K54" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="L54" s="1">
+        <v>6</v>
+      </c>
+      <c r="M54" s="1">
+        <v>40</v>
+      </c>
+      <c r="N54" s="1">
+        <v>11</v>
+      </c>
+      <c r="O54" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="55" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C55" s="1">
+        <v>53012</v>
+      </c>
+      <c r="D55" s="1">
+        <v>7</v>
+      </c>
+      <c r="E55" s="1">
+        <v>10</v>
+      </c>
+      <c r="F55" s="1">
+        <v>5</v>
+      </c>
+      <c r="G55" s="1">
+        <v>3</v>
+      </c>
+      <c r="H55" s="3">
+        <v>3012</v>
+      </c>
+      <c r="I55" s="1">
+        <v>0</v>
+      </c>
+      <c r="J55" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="K55" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="L55" s="1">
+        <v>4</v>
+      </c>
+      <c r="M55" s="1">
+        <v>30</v>
+      </c>
+      <c r="N55" s="1">
+        <v>11</v>
+      </c>
+      <c r="O55" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="56" customFormat="1" customHeight="1"/>
+    <row r="57" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C57" s="1">
+        <v>53102</v>
+      </c>
+      <c r="D57" s="1">
+        <v>7</v>
+      </c>
+      <c r="E57" s="1">
+        <v>50</v>
+      </c>
+      <c r="F57" s="1">
+        <v>5</v>
+      </c>
+      <c r="G57" s="1">
+        <v>3</v>
+      </c>
+      <c r="H57" s="3">
+        <v>3002</v>
+      </c>
+      <c r="I57" s="1">
+        <v>0</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>489</v>
+      </c>
+      <c r="K57" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="L57" s="1">
+        <v>4</v>
+      </c>
+      <c r="M57" s="1">
+        <v>0</v>
+      </c>
+      <c r="N57" s="1">
+        <v>11</v>
+      </c>
+      <c r="O57" s="1">
+        <v>11</v>
+      </c>
+      <c r="P57" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="58" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C58" s="1">
+        <v>53112</v>
+      </c>
+      <c r="D58" s="1">
+        <v>7</v>
+      </c>
+      <c r="E58" s="1">
+        <v>10</v>
+      </c>
+      <c r="F58" s="1">
+        <v>5</v>
+      </c>
+      <c r="G58" s="1">
+        <v>3</v>
+      </c>
+      <c r="H58" s="3">
+        <v>3012</v>
+      </c>
+      <c r="I58" s="1">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="K58" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="L58" s="1">
+        <v>4</v>
+      </c>
+      <c r="M58" s="1">
+        <v>0</v>
+      </c>
+      <c r="N58" s="1">
+        <v>11</v>
+      </c>
+      <c r="O58" s="1">
+        <v>11</v>
+      </c>
+      <c r="P58" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="59" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="H59" s="3"/>
+      <c r="J59" s="3"/>
     </row>
   </sheetData>
   <dataValidations count="1">
